--- a/students.xlsx
+++ b/students.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G3"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -486,7 +486,6 @@
           <t>fsf</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
           <t>3544-04-05</t>
@@ -503,6 +502,39 @@
         </is>
       </c>
       <c r="G3" t="inlineStr">
+        <is>
+          <t>sdgs@gmail.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>derfha</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>ERE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>3000-03-20</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>ST</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>61649464</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
         <is>
           <t>sdgs@gmail.com</t>
         </is>
